--- a/backend/storage/imports/Master_SBM/4. SATUAN BIAYA PEMELIHARAAN SARANA KANTOR.xlsx
+++ b/backend/storage/imports/Master_SBM/4. SATUAN BIAYA PEMELIHARAAN SARANA KANTOR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C7A640-FEE7-4688-8538-38A420968004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CEA8D0-B2A0-424D-8D40-19A541050309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E90E785D-9840-403F-9776-3D4D8C665DB6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>NO</t>
   </si>
@@ -197,20 +197,16 @@
       </rPr>
       <t>Genset  500  KVA</t>
     </r>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="165" formatCode="0."/>
     <numFmt numFmtId="166" formatCode="[$Rp-421]#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -246,7 +242,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -269,11 +265,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -287,20 +292,17 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,51 +627,45 @@
     <col min="4" max="4" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="7">
+        <v>4</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>-1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B3" s="3">
         <v>-2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C3" s="3">
         <v>-3</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D3" s="3">
         <v>-4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
     <row r="4" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
-        <v>4.0999999999999996</v>
+      <c r="A4" s="4">
+        <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -677,13 +673,13 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>80000</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>4.2</v>
+      <c r="A5" s="4">
+        <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -691,13 +687,13 @@
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>730000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>4.3</v>
+      <c r="A6" s="4">
+        <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
@@ -705,13 +701,13 @@
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>690000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>4.4000000000000004</v>
+      <c r="A7" s="4">
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -719,189 +715,189 @@
       <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>610000</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>7190000</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>8640000</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>10150000</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>4.8</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>10780000</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="4">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>13260000</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>14810000</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>4.1100000000000003</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>15850000</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>4.12</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>16790000</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
-        <v>4.13</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>17760000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>20960000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>22960000</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>4.16</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>25620000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>4.17</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>31770000</v>
       </c>
     </row>
